--- a/88/food/2026-01-19-sm.xlsx
+++ b/88/food/2026-01-19-sm.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>МБОУ "Агишбатойская СОШ"</t>
+          <t>МБОУ «Агишбатойская СОШ»</t>
         </is>
       </c>
       <c r="C1" s="39" t="n"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>2026-01-19</t>
         </is>
       </c>
     </row>
